--- a/main/ig/StructureDefinition-dmi-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-transport.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1241,7 +1241,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -1346,7 +1346,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1552,7 +1552,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1760,7 +1760,7 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>117</v>
@@ -1865,7 +1865,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -2071,7 +2071,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2279,7 +2279,7 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>117</v>
@@ -2384,7 +2384,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
@@ -2590,7 +2590,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>81</v>
@@ -2798,7 +2798,7 @@
         <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -2903,7 +2903,7 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>81</v>
@@ -3109,7 +3109,7 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>81</v>
@@ -3317,7 +3317,7 @@
         <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>117</v>
@@ -3422,7 +3422,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>81</v>
@@ -3628,7 +3628,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>81</v>
@@ -3836,7 +3836,7 @@
         <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>117</v>
@@ -3941,7 +3941,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>81</v>
@@ -4147,7 +4147,7 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>81</v>
@@ -4355,7 +4355,7 @@
         <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>117</v>
@@ -4563,7 +4563,7 @@
         <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>117</v>

--- a/main/ig/StructureDefinition-dmi-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1241,7 +1241,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -1346,7 +1346,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1552,7 +1552,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1760,7 +1760,7 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>117</v>
@@ -1865,7 +1865,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -2071,7 +2071,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2279,7 +2279,7 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>117</v>
@@ -2384,7 +2384,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
@@ -2590,7 +2590,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>81</v>
@@ -2798,7 +2798,7 @@
         <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -2903,7 +2903,7 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>81</v>
@@ -3109,7 +3109,7 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>81</v>
@@ -3317,7 +3317,7 @@
         <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>117</v>
@@ -3422,7 +3422,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>81</v>
@@ -3628,7 +3628,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>81</v>
@@ -3836,7 +3836,7 @@
         <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>117</v>
@@ -3941,7 +3941,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>81</v>
@@ -4147,7 +4147,7 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>81</v>
@@ -4355,7 +4355,7 @@
         <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>117</v>
@@ -4563,7 +4563,7 @@
         <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>117</v>

--- a/main/ig/StructureDefinition-dmi-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-transport.xlsx
+++ b/main/ig/StructureDefinition-dmi-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1241,7 +1241,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -1346,7 +1346,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1552,7 +1552,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1760,7 +1760,7 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>117</v>
@@ -1865,7 +1865,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -2071,7 +2071,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2279,7 +2279,7 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>117</v>
@@ -2384,7 +2384,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
@@ -2590,7 +2590,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>81</v>
@@ -2798,7 +2798,7 @@
         <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -2903,7 +2903,7 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>81</v>
@@ -3109,7 +3109,7 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>81</v>
@@ -3317,7 +3317,7 @@
         <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>117</v>
@@ -3422,7 +3422,7 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>81</v>
@@ -3628,7 +3628,7 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>81</v>
@@ -3836,7 +3836,7 @@
         <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>117</v>
@@ -3941,7 +3941,7 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>81</v>
@@ -4147,7 +4147,7 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>81</v>
@@ -4355,7 +4355,7 @@
         <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>117</v>
@@ -4563,7 +4563,7 @@
         <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>117</v>
